--- a/branches/pt/StructureDefinition-package-size.xlsx
+++ b/branches/pt/StructureDefinition-package-size.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-24T21:33:25+00:00</t>
+    <t>2022-08-29T19:31:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
